--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>78.68859278276476</v>
+        <v>12.78689632719927</v>
       </c>
       <c r="D2" t="n">
-        <v>43.01096163287093</v>
+        <v>6.989281265341527</v>
       </c>
       <c r="E2" t="n">
-        <v>12.75595742986498</v>
+        <v>2.072843082353059</v>
       </c>
       <c r="F2" t="n">
-        <v>8.439115448917038</v>
+        <v>1.371356260449019</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.4453967793029</v>
+        <v>7.709876976636721</v>
       </c>
       <c r="D3" t="n">
-        <v>47.49699919901578</v>
+        <v>7.718262369840065</v>
       </c>
       <c r="E3" t="n">
-        <v>12.75595742986498</v>
+        <v>2.072843082353059</v>
       </c>
       <c r="F3" t="n">
-        <v>8.439115448917038</v>
+        <v>1.371356260449019</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.73225248713857</v>
+        <v>10.19399102916002</v>
       </c>
       <c r="D4" t="n">
-        <v>62.72940925866504</v>
+        <v>10.19352900453307</v>
       </c>
       <c r="E4" t="n">
-        <v>12.75595742986498</v>
+        <v>2.072843082353059</v>
       </c>
       <c r="F4" t="n">
-        <v>8.439115448917038</v>
+        <v>1.371356260449019</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
